--- a/vfq-dxp-app/reference/outputs/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
@@ -17,8 +17,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Roles &amp; Credentials'!$A$1:$S$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Applicability Matrix'!$A$2:$G$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Feature Inventory'!$A$1:$J$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Applicability Matrix'!$A$2:$G$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Feature Inventory'!$A$1:$J$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Legacy Crosswalk'!$A$1:$D$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="P23" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q23" s="2" t="n">
         <v>31</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="P24" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q24" s="2" t="n">
         <v>27</v>
@@ -3122,7 +3122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG50"/>
+  <dimension ref="A1:AG52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7232,12 +7232,12 @@
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>Identity / Customer Management</t>
+          <t>Trouble Ticketing / Complaints</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>Passport-to-QID update wizard</t>
+          <t>Ticket Approval Queue</t>
         </is>
       </c>
       <c r="D41" s="18" t="inlineStr">
@@ -7247,74 +7247,46 @@
       </c>
       <c r="E41" s="18" t="inlineStr">
         <is>
-          <t>SCR-151</t>
+          <t>—  (routed directly)</t>
         </is>
       </c>
       <c r="F41" s="18" t="inlineStr">
         <is>
-          <t>Create, Edit, Full</t>
+          <t>Approve</t>
         </is>
       </c>
       <c r="G41" s="18" t="inlineStr"/>
-      <c r="H41" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I41" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J41" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K41" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L41" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H41" s="20" t="n"/>
+      <c r="I41" s="20" t="n"/>
+      <c r="J41" s="20" t="n"/>
+      <c r="K41" s="20" t="n"/>
+      <c r="L41" s="20" t="n"/>
       <c r="M41" s="20" t="n"/>
       <c r="N41" s="20" t="n"/>
       <c r="O41" s="20" t="n"/>
       <c r="P41" s="20" t="n"/>
-      <c r="Q41" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q41" s="20" t="n"/>
       <c r="R41" s="20" t="n"/>
-      <c r="S41" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S41" s="20" t="n"/>
       <c r="T41" s="20" t="n"/>
       <c r="U41" s="20" t="n"/>
-      <c r="V41" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W41" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="V41" s="20" t="n"/>
+      <c r="W41" s="20" t="n"/>
       <c r="X41" s="20" t="n"/>
       <c r="Y41" s="20" t="n"/>
       <c r="Z41" s="20" t="n"/>
       <c r="AA41" s="20" t="n"/>
       <c r="AB41" s="20" t="n"/>
-      <c r="AC41" s="20" t="n"/>
-      <c r="AD41" s="20" t="n"/>
+      <c r="AC41" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AD41" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE41" s="20" t="n"/>
       <c r="AF41" s="20" t="n"/>
       <c r="AG41" s="20" t="n"/>
@@ -7327,27 +7299,27 @@
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>Identity / Customer Management</t>
+          <t>Trouble Ticketing / Complaints</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>Person administration</t>
-        </is>
-      </c>
-      <c r="D42" s="21" t="inlineStr">
-        <is>
-          <t>Planned</t>
+          <t>Ticket approval review + approve/reject/return</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>Built</t>
         </is>
       </c>
       <c r="E42" s="18" t="inlineStr">
         <is>
-          <t>SCR-054</t>
+          <t>—  (routed directly)</t>
         </is>
       </c>
       <c r="F42" s="18" t="inlineStr">
         <is>
-          <t>View, Edit, Full</t>
+          <t>Approve</t>
         </is>
       </c>
       <c r="G42" s="18" t="inlineStr"/>
@@ -7365,28 +7337,24 @@
       <c r="S42" s="20" t="n"/>
       <c r="T42" s="20" t="n"/>
       <c r="U42" s="20" t="n"/>
-      <c r="V42" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W42" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="V42" s="20" t="n"/>
+      <c r="W42" s="20" t="n"/>
       <c r="X42" s="20" t="n"/>
       <c r="Y42" s="20" t="n"/>
       <c r="Z42" s="20" t="n"/>
       <c r="AA42" s="20" t="n"/>
       <c r="AB42" s="20" t="n"/>
-      <c r="AC42" s="20" t="n"/>
-      <c r="AD42" s="20" t="n"/>
-      <c r="AE42" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC42" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AD42" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AE42" s="20" t="n"/>
       <c r="AF42" s="20" t="n"/>
       <c r="AG42" s="20" t="n"/>
     </row>
@@ -7403,40 +7371,72 @@
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>Agent 360 / asset summary</t>
-        </is>
-      </c>
-      <c r="D43" s="21" t="inlineStr">
-        <is>
-          <t>Planned</t>
+          <t>Passport-to-QID update wizard</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>Built</t>
         </is>
       </c>
       <c r="E43" s="18" t="inlineStr">
         <is>
-          <t>SCR-022</t>
+          <t>SCR-151</t>
         </is>
       </c>
       <c r="F43" s="18" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Create, Edit, Full</t>
         </is>
       </c>
       <c r="G43" s="18" t="inlineStr"/>
-      <c r="H43" s="20" t="n"/>
-      <c r="I43" s="20" t="n"/>
-      <c r="J43" s="20" t="n"/>
-      <c r="K43" s="20" t="n"/>
-      <c r="L43" s="20" t="n"/>
+      <c r="H43" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I43" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J43" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K43" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L43" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M43" s="20" t="n"/>
       <c r="N43" s="20" t="n"/>
       <c r="O43" s="20" t="n"/>
       <c r="P43" s="20" t="n"/>
-      <c r="Q43" s="20" t="n"/>
+      <c r="Q43" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R43" s="20" t="n"/>
-      <c r="S43" s="20" t="n"/>
+      <c r="S43" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T43" s="20" t="n"/>
       <c r="U43" s="20" t="n"/>
-      <c r="V43" s="20" t="n"/>
+      <c r="V43" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="W43" s="19" t="inlineStr">
         <is>
           <t>✓</t>
@@ -7461,49 +7461,37 @@
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>Enterprise / IoT / B2B</t>
+          <t>Identity / Customer Management</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>Enterprise account creation</t>
-        </is>
-      </c>
-      <c r="D44" s="18" t="inlineStr">
-        <is>
-          <t>Built</t>
+          <t>Person administration</t>
+        </is>
+      </c>
+      <c r="D44" s="21" t="inlineStr">
+        <is>
+          <t>Planned</t>
         </is>
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>SCR-007</t>
+          <t>SCR-054</t>
         </is>
       </c>
       <c r="F44" s="18" t="inlineStr">
         <is>
-          <t>Create</t>
+          <t>View, Edit, Full</t>
         </is>
       </c>
       <c r="G44" s="18" t="inlineStr"/>
       <c r="H44" s="20" t="n"/>
       <c r="I44" s="20" t="n"/>
-      <c r="J44" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J44" s="20" t="n"/>
       <c r="K44" s="20" t="n"/>
       <c r="L44" s="20" t="n"/>
-      <c r="M44" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N44" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M44" s="20" t="n"/>
+      <c r="N44" s="20" t="n"/>
       <c r="O44" s="20" t="n"/>
       <c r="P44" s="20" t="n"/>
       <c r="Q44" s="20" t="n"/>
@@ -7511,8 +7499,16 @@
       <c r="S44" s="20" t="n"/>
       <c r="T44" s="20" t="n"/>
       <c r="U44" s="20" t="n"/>
-      <c r="V44" s="20" t="n"/>
-      <c r="W44" s="20" t="n"/>
+      <c r="V44" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W44" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="X44" s="20" t="n"/>
       <c r="Y44" s="20" t="n"/>
       <c r="Z44" s="20" t="n"/>
@@ -7520,7 +7516,11 @@
       <c r="AB44" s="20" t="n"/>
       <c r="AC44" s="20" t="n"/>
       <c r="AD44" s="20" t="n"/>
-      <c r="AE44" s="20" t="n"/>
+      <c r="AE44" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF44" s="20" t="n"/>
       <c r="AG44" s="20" t="n"/>
     </row>
@@ -7532,27 +7532,27 @@
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>Enterprise / IoT / B2B</t>
+          <t>Identity / Customer Management</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>Bulk adjustment portal</t>
-        </is>
-      </c>
-      <c r="D45" s="18" t="inlineStr">
-        <is>
-          <t>Built</t>
+          <t>Agent 360 / asset summary</t>
+        </is>
+      </c>
+      <c r="D45" s="21" t="inlineStr">
+        <is>
+          <t>Planned</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr">
         <is>
-          <t>SCR-001</t>
+          <t>SCR-022</t>
         </is>
       </c>
       <c r="F45" s="18" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G45" s="18" t="inlineStr"/>
@@ -7561,16 +7561,8 @@
       <c r="J45" s="20" t="n"/>
       <c r="K45" s="20" t="n"/>
       <c r="L45" s="20" t="n"/>
-      <c r="M45" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N45" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M45" s="20" t="n"/>
+      <c r="N45" s="20" t="n"/>
       <c r="O45" s="20" t="n"/>
       <c r="P45" s="20" t="n"/>
       <c r="Q45" s="20" t="n"/>
@@ -7578,18 +7570,14 @@
       <c r="S45" s="20" t="n"/>
       <c r="T45" s="20" t="n"/>
       <c r="U45" s="20" t="n"/>
-      <c r="V45" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W45" s="20" t="n"/>
+      <c r="V45" s="20" t="n"/>
+      <c r="W45" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="X45" s="20" t="n"/>
-      <c r="Y45" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y45" s="20" t="n"/>
       <c r="Z45" s="20" t="n"/>
       <c r="AA45" s="20" t="n"/>
       <c r="AB45" s="20" t="n"/>
@@ -7612,22 +7600,22 @@
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>Billing profile grid (account level)</t>
-        </is>
-      </c>
-      <c r="D46" s="21" t="inlineStr">
-        <is>
-          <t>Planned</t>
+          <t>Enterprise account creation</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>Built</t>
         </is>
       </c>
       <c r="E46" s="18" t="inlineStr">
         <is>
-          <t>SCR-186</t>
+          <t>SCR-007</t>
         </is>
       </c>
       <c r="F46" s="18" t="inlineStr">
         <is>
-          <t>View, Edit</t>
+          <t>Create</t>
         </is>
       </c>
       <c r="G46" s="18" t="inlineStr"/>
@@ -7653,27 +7641,15 @@
       <c r="O46" s="20" t="n"/>
       <c r="P46" s="20" t="n"/>
       <c r="Q46" s="20" t="n"/>
-      <c r="R46" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R46" s="20" t="n"/>
       <c r="S46" s="20" t="n"/>
       <c r="T46" s="20" t="n"/>
       <c r="U46" s="20" t="n"/>
       <c r="V46" s="20" t="n"/>
       <c r="W46" s="20" t="n"/>
       <c r="X46" s="20" t="n"/>
-      <c r="Y46" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z46" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y46" s="20" t="n"/>
+      <c r="Z46" s="20" t="n"/>
       <c r="AA46" s="20" t="n"/>
       <c r="AB46" s="20" t="n"/>
       <c r="AC46" s="20" t="n"/>
@@ -7690,27 +7666,27 @@
       </c>
       <c r="B47" s="18" t="inlineStr">
         <is>
-          <t>Billing &amp; Adjustments</t>
+          <t>Enterprise / IoT / B2B</t>
         </is>
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>Statement of Account view</t>
-        </is>
-      </c>
-      <c r="D47" s="21" t="inlineStr">
-        <is>
-          <t>Planned</t>
+          <t>Bulk adjustment portal</t>
+        </is>
+      </c>
+      <c r="D47" s="18" t="inlineStr">
+        <is>
+          <t>Built</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr">
         <is>
-          <t>SCR-003</t>
+          <t>SCR-001</t>
         </is>
       </c>
       <c r="F47" s="18" t="inlineStr">
         <is>
-          <t>View, Edit</t>
+          <t>Edit</t>
         </is>
       </c>
       <c r="G47" s="18" t="inlineStr"/>
@@ -7730,29 +7706,17 @@
         </is>
       </c>
       <c r="O47" s="20" t="n"/>
-      <c r="P47" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q47" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R47" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P47" s="20" t="n"/>
+      <c r="Q47" s="20" t="n"/>
+      <c r="R47" s="20" t="n"/>
+      <c r="S47" s="20" t="n"/>
       <c r="T47" s="20" t="n"/>
       <c r="U47" s="20" t="n"/>
-      <c r="V47" s="20" t="n"/>
+      <c r="V47" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="W47" s="20" t="n"/>
       <c r="X47" s="20" t="n"/>
       <c r="Y47" s="19" t="inlineStr">
@@ -7760,30 +7724,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Z47" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Z47" s="20" t="n"/>
       <c r="AA47" s="20" t="n"/>
       <c r="AB47" s="20" t="n"/>
-      <c r="AC47" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD47" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC47" s="20" t="n"/>
+      <c r="AD47" s="20" t="n"/>
       <c r="AE47" s="20" t="n"/>
       <c r="AF47" s="20" t="n"/>
-      <c r="AG47" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG47" s="20" t="n"/>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="17" t="inlineStr">
@@ -7793,12 +7741,12 @@
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>Billing &amp; Adjustments</t>
+          <t>Enterprise / IoT / B2B</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>Bill simulation</t>
+          <t>Billing profile grid (account level)</t>
         </is>
       </c>
       <c r="D48" s="21" t="inlineStr">
@@ -7808,7 +7756,7 @@
       </c>
       <c r="E48" s="18" t="inlineStr">
         <is>
-          <t>SCR-005</t>
+          <t>SCR-186</t>
         </is>
       </c>
       <c r="F48" s="18" t="inlineStr">
@@ -7819,15 +7767,31 @@
       <c r="G48" s="18" t="inlineStr"/>
       <c r="H48" s="20" t="n"/>
       <c r="I48" s="20" t="n"/>
-      <c r="J48" s="20" t="n"/>
+      <c r="J48" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K48" s="20" t="n"/>
       <c r="L48" s="20" t="n"/>
-      <c r="M48" s="20" t="n"/>
-      <c r="N48" s="20" t="n"/>
+      <c r="M48" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N48" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O48" s="20" t="n"/>
       <c r="P48" s="20" t="n"/>
       <c r="Q48" s="20" t="n"/>
-      <c r="R48" s="20" t="n"/>
+      <c r="R48" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S48" s="20" t="n"/>
       <c r="T48" s="20" t="n"/>
       <c r="U48" s="20" t="n"/>
@@ -7860,12 +7824,12 @@
       </c>
       <c r="B49" s="18" t="inlineStr">
         <is>
-          <t>CAF, Attachments &amp; Forms</t>
+          <t>Billing &amp; Adjustments</t>
         </is>
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>Product promotions administration</t>
+          <t>Statement of Account view</t>
         </is>
       </c>
       <c r="D49" s="21" t="inlineStr">
@@ -7875,12 +7839,12 @@
       </c>
       <c r="E49" s="18" t="inlineStr">
         <is>
-          <t>SCR-117, SCR-118</t>
+          <t>SCR-003</t>
         </is>
       </c>
       <c r="F49" s="18" t="inlineStr">
         <is>
-          <t>Edit, Full</t>
+          <t>View, Edit</t>
         </is>
       </c>
       <c r="G49" s="18" t="inlineStr"/>
@@ -7889,39 +7853,71 @@
       <c r="J49" s="20" t="n"/>
       <c r="K49" s="20" t="n"/>
       <c r="L49" s="20" t="n"/>
-      <c r="M49" s="20" t="n"/>
-      <c r="N49" s="20" t="n"/>
-      <c r="O49" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P49" s="20" t="n"/>
-      <c r="Q49" s="20" t="n"/>
-      <c r="R49" s="20" t="n"/>
-      <c r="S49" s="20" t="n"/>
+      <c r="M49" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N49" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O49" s="20" t="n"/>
+      <c r="P49" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q49" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T49" s="20" t="n"/>
       <c r="U49" s="20" t="n"/>
       <c r="V49" s="20" t="n"/>
       <c r="W49" s="20" t="n"/>
       <c r="X49" s="20" t="n"/>
-      <c r="Y49" s="20" t="n"/>
-      <c r="Z49" s="20" t="n"/>
+      <c r="Y49" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z49" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AA49" s="20" t="n"/>
       <c r="AB49" s="20" t="n"/>
-      <c r="AC49" s="20" t="n"/>
+      <c r="AC49" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD49" s="19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AE49" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE49" s="20" t="n"/>
       <c r="AF49" s="20" t="n"/>
-      <c r="AG49" s="20" t="n"/>
+      <c r="AG49" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="17" t="inlineStr">
@@ -7931,12 +7927,12 @@
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>Platform Governance &amp; Architecture</t>
+          <t>Billing &amp; Adjustments</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>Integration / service bus monitor</t>
+          <t>Bill simulation</t>
         </is>
       </c>
       <c r="D50" s="21" t="inlineStr">
@@ -7946,12 +7942,12 @@
       </c>
       <c r="E50" s="18" t="inlineStr">
         <is>
-          <t>SCR-016, SCR-065</t>
+          <t>SCR-005</t>
         </is>
       </c>
       <c r="F50" s="18" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>View, Edit</t>
         </is>
       </c>
       <c r="G50" s="18" t="inlineStr"/>
@@ -7972,22 +7968,160 @@
       <c r="V50" s="20" t="n"/>
       <c r="W50" s="20" t="n"/>
       <c r="X50" s="20" t="n"/>
-      <c r="Y50" s="20" t="n"/>
-      <c r="Z50" s="20" t="n"/>
+      <c r="Y50" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z50" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AA50" s="20" t="n"/>
       <c r="AB50" s="20" t="n"/>
       <c r="AC50" s="20" t="n"/>
       <c r="AD50" s="20" t="n"/>
-      <c r="AE50" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE50" s="20" t="n"/>
       <c r="AF50" s="20" t="n"/>
       <c r="AG50" s="20" t="n"/>
     </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>FEAT-049</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="inlineStr">
+        <is>
+          <t>CAF, Attachments &amp; Forms</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>Product promotions administration</t>
+        </is>
+      </c>
+      <c r="D51" s="21" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="inlineStr">
+        <is>
+          <t>SCR-117, SCR-118</t>
+        </is>
+      </c>
+      <c r="F51" s="18" t="inlineStr">
+        <is>
+          <t>Edit, Full</t>
+        </is>
+      </c>
+      <c r="G51" s="18" t="inlineStr"/>
+      <c r="H51" s="20" t="n"/>
+      <c r="I51" s="20" t="n"/>
+      <c r="J51" s="20" t="n"/>
+      <c r="K51" s="20" t="n"/>
+      <c r="L51" s="20" t="n"/>
+      <c r="M51" s="20" t="n"/>
+      <c r="N51" s="20" t="n"/>
+      <c r="O51" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P51" s="20" t="n"/>
+      <c r="Q51" s="20" t="n"/>
+      <c r="R51" s="20" t="n"/>
+      <c r="S51" s="20" t="n"/>
+      <c r="T51" s="20" t="n"/>
+      <c r="U51" s="20" t="n"/>
+      <c r="V51" s="20" t="n"/>
+      <c r="W51" s="20" t="n"/>
+      <c r="X51" s="20" t="n"/>
+      <c r="Y51" s="20" t="n"/>
+      <c r="Z51" s="20" t="n"/>
+      <c r="AA51" s="20" t="n"/>
+      <c r="AB51" s="20" t="n"/>
+      <c r="AC51" s="20" t="n"/>
+      <c r="AD51" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AE51" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AF51" s="20" t="n"/>
+      <c r="AG51" s="20" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>FEAT-050</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>Platform Governance &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>Integration / service bus monitor</t>
+        </is>
+      </c>
+      <c r="D52" s="21" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E52" s="18" t="inlineStr">
+        <is>
+          <t>SCR-016, SCR-065</t>
+        </is>
+      </c>
+      <c r="F52" s="18" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="G52" s="18" t="inlineStr"/>
+      <c r="H52" s="20" t="n"/>
+      <c r="I52" s="20" t="n"/>
+      <c r="J52" s="20" t="n"/>
+      <c r="K52" s="20" t="n"/>
+      <c r="L52" s="20" t="n"/>
+      <c r="M52" s="20" t="n"/>
+      <c r="N52" s="20" t="n"/>
+      <c r="O52" s="20" t="n"/>
+      <c r="P52" s="20" t="n"/>
+      <c r="Q52" s="20" t="n"/>
+      <c r="R52" s="20" t="n"/>
+      <c r="S52" s="20" t="n"/>
+      <c r="T52" s="20" t="n"/>
+      <c r="U52" s="20" t="n"/>
+      <c r="V52" s="20" t="n"/>
+      <c r="W52" s="20" t="n"/>
+      <c r="X52" s="20" t="n"/>
+      <c r="Y52" s="20" t="n"/>
+      <c r="Z52" s="20" t="n"/>
+      <c r="AA52" s="20" t="n"/>
+      <c r="AB52" s="20" t="n"/>
+      <c r="AC52" s="20" t="n"/>
+      <c r="AD52" s="20" t="n"/>
+      <c r="AE52" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AF52" s="20" t="n"/>
+      <c r="AG52" s="20" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:G50"/>
+  <autoFilter ref="A2:G52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9315,7 +9449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11162,22 +11296,22 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>identity.passport-to-qid</t>
+          <t>tickets.approval-queue</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Passport-to-QID update wizard</t>
+          <t>Ticket Approval Queue</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Identity / Customer Management</t>
+          <t>Trouble Ticketing / Complaints</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>module</t>
+          <t>workspace</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -11187,15 +11321,15 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>SCR-151</t>
+          <t>—  (routed directly)</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Create, Edit, Full</t>
+          <t>Approve</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr"/>
@@ -11208,40 +11342,40 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>identity.person-administration</t>
+          <t>tickets.approval-detail</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Person administration</t>
+          <t>Ticket approval review + approve/reject/return</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Identity / Customer Management</t>
+          <t>Trouble Ticketing / Complaints</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>module</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>Planned</t>
+          <t>workspace</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Built</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>SCR-054</t>
+          <t>—  (routed directly)</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>View, Edit, Full</t>
+          <t>Approve</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr"/>
@@ -11254,12 +11388,12 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>identity.agent-360-asset-summary</t>
+          <t>identity.passport-to-qid</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Agent 360 / asset summary</t>
+          <t>Passport-to-QID update wizard</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -11272,22 +11406,22 @@
           <t>module</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Built</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>SCR-022</t>
+          <t>SCR-151</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Create, Edit, Full</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr"/>
@@ -11300,17 +11434,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>enterprise.account-creation</t>
+          <t>identity.person-administration</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Enterprise account creation</t>
+          <t>Person administration</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Enterprise / IoT / B2B</t>
+          <t>Identity / Customer Management</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -11318,14 +11452,14 @@
           <t>module</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Built</t>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>Planned</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>SCR-007</t>
+          <t>SCR-054</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
@@ -11333,7 +11467,7 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Create</t>
+          <t>View, Edit, Full</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr"/>
@@ -11346,17 +11480,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>enterprise.bulk-adjustment-portal</t>
+          <t>identity.agent-360-asset-summary</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Bulk adjustment portal</t>
+          <t>Agent 360 / asset summary</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Enterprise / IoT / B2B</t>
+          <t>Identity / Customer Management</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -11364,22 +11498,22 @@
           <t>module</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Built</t>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>Planned</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>SCR-001</t>
+          <t>SCR-022</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>View</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr"/>
@@ -11392,12 +11526,12 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>enterprise.billing-profile-grid</t>
+          <t>enterprise.account-creation</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Billing profile grid (account level)</t>
+          <t>Enterprise account creation</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -11410,22 +11544,22 @@
           <t>module</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Built</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>SCR-186</t>
+          <t>SCR-007</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>View, Edit</t>
+          <t>Create</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr"/>
@@ -11438,17 +11572,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>billing.statement-of-account</t>
+          <t>enterprise.bulk-adjustment-portal</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Statement of Account view</t>
+          <t>Bulk adjustment portal</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Billing &amp; Adjustments</t>
+          <t>Enterprise / IoT / B2B</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -11456,22 +11590,22 @@
           <t>module</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Built</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>SCR-003</t>
+          <t>SCR-001</t>
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>View, Edit</t>
+          <t>Edit</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr"/>
@@ -11484,17 +11618,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>billing.bill-simulation</t>
+          <t>enterprise.billing-profile-grid</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Bill simulation</t>
+          <t>Billing profile grid (account level)</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Billing &amp; Adjustments</t>
+          <t>Enterprise / IoT / B2B</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -11509,11 +11643,11 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>SCR-005</t>
+          <t>SCR-186</t>
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
@@ -11530,17 +11664,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>admin.product-promotions</t>
+          <t>billing.statement-of-account</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Product promotions administration</t>
+          <t>Statement of Account view</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>CAF, Attachments &amp; Forms</t>
+          <t>Billing &amp; Adjustments</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -11555,15 +11689,15 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>SCR-117, SCR-118</t>
+          <t>SCR-003</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Edit, Full</t>
+          <t>View, Edit</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr"/>
@@ -11576,46 +11710,138 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
+          <t>billing.bill-simulation</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Bill simulation</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Billing &amp; Adjustments</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>module</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>SCR-005</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>View, Edit</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>FEAT-049</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>admin.product-promotions</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Product promotions administration</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>CAF, Attachments &amp; Forms</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>module</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>SCR-117, SCR-118</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Edit, Full</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>FEAT-050</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
           <t>platform.integration-monitor</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>Integration / service bus monitor</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>Platform Governance &amp; Architecture</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>SCR-016, SCR-065</t>
         </is>
       </c>
-      <c r="H49" s="2" t="n">
+      <c r="H51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="J49" s="5" t="inlineStr"/>
+      <c r="J51" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J49"/>
+  <autoFilter ref="A1:J51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15695,7 +15921,7 @@
       </c>
       <c r="B31" s="33" t="inlineStr">
         <is>
-          <t>48 catalogued (35 built, 13 planned).</t>
+          <t>50 catalogued (37 built, 13 planned).</t>
         </is>
       </c>
     </row>
@@ -15786,7 +16012,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6da4fa1</t>
+          <t>aa69142</t>
         </is>
       </c>
     </row>

--- a/vfq-dxp-app/reference/outputs/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
@@ -16012,7 +16012,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>aa69142</t>
+          <t>3d0d2a2</t>
         </is>
       </c>
     </row>

--- a/vfq-dxp-app/reference/outputs/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
@@ -16012,7 +16012,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3d0d2a2</t>
+          <t>e74dc45</t>
         </is>
       </c>
     </row>

--- a/vfq-dxp-app/reference/outputs/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
@@ -16012,7 +16012,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>e74dc45</t>
+          <t>c2d6403</t>
         </is>
       </c>
     </row>

--- a/vfq-dxp-app/reference/outputs/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
@@ -16012,7 +16012,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>c2d6403</t>
+          <t>a2a1e01</t>
         </is>
       </c>
     </row>

--- a/vfq-dxp-app/reference/outputs/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
@@ -16012,7 +16012,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>a2a1e01</t>
+          <t>3949fbf</t>
         </is>
       </c>
     </row>

--- a/vfq-dxp-app/reference/outputs/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
@@ -16012,7 +16012,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3949fbf</t>
+          <t>8be22a7</t>
         </is>
       </c>
     </row>

--- a/vfq-dxp-app/reference/outputs/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
+++ b/vfq-dxp-app/reference/outputs/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
@@ -16012,7 +16012,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>8be22a7</t>
+          <t>c5f67be</t>
         </is>
       </c>
     </row>
